--- a/WWW/data/Localizaciones.corr.xlsx
+++ b/WWW/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8F3C82-B9B8-4684-AF65-B93CF2DDD80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF55A1EB-1855-412C-9F53-665C059B8862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6108" yWindow="3744" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="61">
   <si>
     <t>address</t>
   </si>
@@ -344,7 +344,44 @@
     <t>CL 49 A 78 A 39</t>
   </si>
   <si>
-    <t>CR 115 A 64 CC 4</t>
+    <r>
+      <t>CL 5 S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 25 233</t>
+    </r>
+  </si>
+  <si>
+    <t>Ciudad</t>
+  </si>
+  <si>
+    <t>MEDELLIN</t>
+  </si>
+  <si>
+    <t>ENVIGADO</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
   </si>
 </sst>
 </file>
@@ -764,17 +801,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
     <col min="6" max="6" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -787,8 +825,11 @@
       <c r="D1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -801,8 +842,11 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -815,8 +859,11 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -829,8 +876,11 @@
       <c r="D4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -843,8 +893,11 @@
       <c r="D5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -857,8 +910,11 @@
       <c r="D6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -871,8 +927,11 @@
       <c r="D7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -885,8 +944,11 @@
       <c r="D8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -899,8 +961,11 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -913,8 +978,11 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -927,8 +995,11 @@
       <c r="D11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -941,8 +1012,11 @@
       <c r="D12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -955,8 +1029,11 @@
       <c r="D13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -969,8 +1046,11 @@
       <c r="D14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -983,8 +1063,11 @@
       <c r="D15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -996,6 +1079,9 @@
       </c>
       <c r="D16" t="s">
         <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1011,6 +1097,9 @@
       <c r="D17" t="s">
         <v>11</v>
       </c>
+      <c r="E17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1025,6 +1114,9 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
+      <c r="E18" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -1039,6 +1131,9 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1053,6 +1148,9 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -1067,6 +1165,9 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
+      <c r="E21" t="s">
+        <v>57</v>
+      </c>
       <c r="F21" s="9"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1082,6 +1183,9 @@
       <c r="D22" t="s">
         <v>27</v>
       </c>
+      <c r="E22" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1096,6 +1200,9 @@
       <c r="D23" t="s">
         <v>27</v>
       </c>
+      <c r="E23" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1110,6 +1217,9 @@
       <c r="D24" t="s">
         <v>30</v>
       </c>
+      <c r="E24" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1124,6 +1234,9 @@
       <c r="D25" t="s">
         <v>30</v>
       </c>
+      <c r="E25" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1138,6 +1251,9 @@
       <c r="D26" t="s">
         <v>30</v>
       </c>
+      <c r="E26" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1152,6 +1268,9 @@
       <c r="D27" t="s">
         <v>30</v>
       </c>
+      <c r="E27" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1166,6 +1285,9 @@
       <c r="D28" t="s">
         <v>30</v>
       </c>
+      <c r="E28" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1180,6 +1302,9 @@
       <c r="D29" t="s">
         <v>30</v>
       </c>
+      <c r="E29" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1194,6 +1319,9 @@
       <c r="D30" t="s">
         <v>30</v>
       </c>
+      <c r="E30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1208,6 +1336,9 @@
       <c r="D31" t="s">
         <v>30</v>
       </c>
+      <c r="E31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -1222,8 +1353,11 @@
       <c r="D32" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -1236,8 +1370,11 @@
       <c r="D33" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -1250,10 +1387,13 @@
       <c r="D34" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B35" s="11">
         <v>6.1931741895951999</v>
@@ -1264,8 +1404,11 @@
       <c r="D35" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1279,8 +1422,11 @@
       <c r="D36" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -1293,8 +1439,11 @@
       <c r="D37" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1307,8 +1456,11 @@
       <c r="D38" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1321,8 +1473,11 @@
       <c r="D39" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1335,8 +1490,11 @@
       <c r="D40" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1349,8 +1507,11 @@
       <c r="D41" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1363,8 +1524,11 @@
       <c r="D42" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1377,8 +1541,11 @@
       <c r="D43" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1391,8 +1558,11 @@
       <c r="D44" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1405,8 +1575,11 @@
       <c r="D45" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1419,8 +1592,11 @@
       <c r="D46" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1433,8 +1609,11 @@
       <c r="D47" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1447,8 +1626,11 @@
       <c r="D48" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1461,19 +1643,8 @@
       <c r="D49" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="10">
-        <v>6.2857269606122097</v>
-      </c>
-      <c r="C50">
-        <v>-75.607147916904196</v>
-      </c>
-      <c r="D50" t="s">
-        <v>53</v>
+      <c r="E49" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/WWW/data/Localizaciones.corr.xlsx
+++ b/WWW/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF55A1EB-1855-412C-9F53-665C059B8862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8F3C82-B9B8-4684-AF65-B93CF2DDD80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6108" yWindow="3744" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
   <si>
     <t>address</t>
   </si>
@@ -344,44 +344,7 @@
     <t>CL 49 A 78 A 39</t>
   </si>
   <si>
-    <r>
-      <t>CL 5 S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>UR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 25 233</t>
-    </r>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>MEDELLIN</t>
-  </si>
-  <si>
-    <t>ENVIGADO</t>
-  </si>
-  <si>
-    <t>SABANETA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
+    <t>CR 115 A 64 CC 4</t>
   </si>
 </sst>
 </file>
@@ -801,18 +764,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="1"/>
     <col min="6" max="6" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -825,11 +787,8 @@
       <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -842,11 +801,8 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -859,11 +815,8 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -876,11 +829,8 @@
       <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -893,11 +843,8 @@
       <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -910,11 +857,8 @@
       <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -927,11 +871,8 @@
       <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -944,11 +885,8 @@
       <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -961,11 +899,8 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -978,11 +913,8 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -995,11 +927,8 @@
       <c r="D11" t="s">
         <v>11</v>
       </c>
-      <c r="E11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1012,11 +941,8 @@
       <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="E12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1029,11 +955,8 @@
       <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1046,11 +969,8 @@
       <c r="D14" t="s">
         <v>11</v>
       </c>
-      <c r="E14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1063,11 +983,8 @@
       <c r="D15" t="s">
         <v>11</v>
       </c>
-      <c r="E15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1079,9 +996,6 @@
       </c>
       <c r="D16" t="s">
         <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1097,9 +1011,6 @@
       <c r="D17" t="s">
         <v>11</v>
       </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1114,9 +1025,6 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
-      <c r="E18" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -1131,9 +1039,6 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
-      <c r="E19" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1148,9 +1053,6 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
-      <c r="E20" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -1165,9 +1067,6 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="E21" t="s">
-        <v>57</v>
-      </c>
       <c r="F21" s="9"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1183,9 +1082,6 @@
       <c r="D22" t="s">
         <v>27</v>
       </c>
-      <c r="E22" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1200,9 +1096,6 @@
       <c r="D23" t="s">
         <v>27</v>
       </c>
-      <c r="E23" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1217,9 +1110,6 @@
       <c r="D24" t="s">
         <v>30</v>
       </c>
-      <c r="E24" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1234,9 +1124,6 @@
       <c r="D25" t="s">
         <v>30</v>
       </c>
-      <c r="E25" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1251,9 +1138,6 @@
       <c r="D26" t="s">
         <v>30</v>
       </c>
-      <c r="E26" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1268,9 +1152,6 @@
       <c r="D27" t="s">
         <v>30</v>
       </c>
-      <c r="E27" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1285,9 +1166,6 @@
       <c r="D28" t="s">
         <v>30</v>
       </c>
-      <c r="E28" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1302,9 +1180,6 @@
       <c r="D29" t="s">
         <v>30</v>
       </c>
-      <c r="E29" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1319,9 +1194,6 @@
       <c r="D30" t="s">
         <v>30</v>
       </c>
-      <c r="E30" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1336,9 +1208,6 @@
       <c r="D31" t="s">
         <v>30</v>
       </c>
-      <c r="E31" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -1353,11 +1222,8 @@
       <c r="D32" t="s">
         <v>30</v>
       </c>
-      <c r="E32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -1370,11 +1236,8 @@
       <c r="D33" t="s">
         <v>30</v>
       </c>
-      <c r="E33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -1387,13 +1250,10 @@
       <c r="D34" t="s">
         <v>30</v>
       </c>
-      <c r="E34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B35" s="11">
         <v>6.1931741895951999</v>
@@ -1404,11 +1264,8 @@
       <c r="D35" t="s">
         <v>30</v>
       </c>
-      <c r="E35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1422,11 +1279,8 @@
       <c r="D36" t="s">
         <v>30</v>
       </c>
-      <c r="E36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -1439,11 +1293,8 @@
       <c r="D37" t="s">
         <v>30</v>
       </c>
-      <c r="E37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1456,11 +1307,8 @@
       <c r="D38" t="s">
         <v>30</v>
       </c>
-      <c r="E38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1473,11 +1321,8 @@
       <c r="D39" t="s">
         <v>30</v>
       </c>
-      <c r="E39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1490,11 +1335,8 @@
       <c r="D40" t="s">
         <v>30</v>
       </c>
-      <c r="E40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1507,11 +1349,8 @@
       <c r="D41" t="s">
         <v>30</v>
       </c>
-      <c r="E41" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1524,11 +1363,8 @@
       <c r="D42" t="s">
         <v>30</v>
       </c>
-      <c r="E42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1541,11 +1377,8 @@
       <c r="D43" t="s">
         <v>30</v>
       </c>
-      <c r="E43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1558,11 +1391,8 @@
       <c r="D44" t="s">
         <v>30</v>
       </c>
-      <c r="E44" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1575,11 +1405,8 @@
       <c r="D45" t="s">
         <v>30</v>
       </c>
-      <c r="E45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1592,11 +1419,8 @@
       <c r="D46" t="s">
         <v>30</v>
       </c>
-      <c r="E46" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1609,11 +1433,8 @@
       <c r="D47" t="s">
         <v>53</v>
       </c>
-      <c r="E47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1626,11 +1447,8 @@
       <c r="D48" t="s">
         <v>53</v>
       </c>
-      <c r="E48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1643,8 +1461,19 @@
       <c r="D49" t="s">
         <v>51</v>
       </c>
-      <c r="E49" t="s">
-        <v>60</v>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="10">
+        <v>6.2857269606122097</v>
+      </c>
+      <c r="C50">
+        <v>-75.607147916904196</v>
+      </c>
+      <c r="D50" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
